--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121378966</v>
+        <v>121380829</v>
       </c>
       <c r="B3" t="n">
-        <v>77534</v>
+        <v>90644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6000248</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536122</v>
+        <v>536023</v>
       </c>
       <c r="R3" t="n">
-        <v>6663736</v>
+        <v>6663863</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grankåda i lång stamskada.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,6 +883,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -897,17 +907,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121380560</v>
+        <v>121377665</v>
       </c>
       <c r="B4" t="n">
-        <v>74517</v>
+        <v>56404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +930,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>100045</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536014</v>
+        <v>536173</v>
       </c>
       <c r="R4" t="n">
-        <v>6663853</v>
+        <v>6663536</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,21 +1019,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1029,17 +1028,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121377665</v>
+        <v>121381688</v>
       </c>
       <c r="B5" t="n">
-        <v>56401</v>
+        <v>90662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,43 +1051,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100045</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536173</v>
+        <v>536047</v>
       </c>
       <c r="R5" t="n">
-        <v>6663536</v>
+        <v>6663867</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,6 +1131,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1150,10 +1155,1889 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121377259</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57720</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>536132</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6663471</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121381754</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>536061</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6663870</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På senvuxen gran i sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121379825</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>536119</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6663816</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121378966</v>
+      </c>
+      <c r="B9" t="n">
+        <v>77537</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>536122</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6663736</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121379908</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>535988</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6663825</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121379915</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>536016</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6663828</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Knärot. Snitslat av SKS</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121400775</v>
+      </c>
+      <c r="B12" t="n">
+        <v>77550</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6003412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Röd kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis zebrina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Rikkinen &amp; Tuovila</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>536121</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6663736</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121379200</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43707</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>536184</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6663844</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121377312</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>536183</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6663507</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 fröställningar.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121377626</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>536173</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6663536</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>En vinterståndare. Fler plantor.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121380560</v>
+      </c>
+      <c r="B16" t="n">
+        <v>74520</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>536014</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6663853</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grov klibbal 54 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121379027</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>536126</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6663835</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS. Vid stort block.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121381766</v>
+      </c>
+      <c r="B18" t="n">
+        <v>74647</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>536080</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6663854</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121381773</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57717</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>536080</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6663854</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
           <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121400778</v>
+      </c>
+      <c r="B20" t="n">
+        <v>77537</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>536121</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6663736</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121380829</v>
+        <v>121400775</v>
       </c>
       <c r="B3" t="n">
-        <v>90644</v>
+        <v>77550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>6003412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Röd kådsvartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenothecopsis zebrina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Rikkinen &amp; Tuovila</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536023</v>
+        <v>536121</v>
       </c>
       <c r="R3" t="n">
-        <v>6663863</v>
+        <v>6663736</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,22 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,9 +879,15 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>gran</t>
@@ -896,28 +900,28 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kåda # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121377665</v>
+        <v>121378966</v>
       </c>
       <c r="B4" t="n">
-        <v>56404</v>
+        <v>77537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,47 +930,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100045</v>
+        <v>6000248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536173</v>
+        <v>536122</v>
       </c>
       <c r="R4" t="n">
-        <v>6663536</v>
+        <v>6663736</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1006,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +1020,35 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1162,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121377259</v>
+        <v>121377312</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,41 +1202,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536132</v>
+        <v>536183</v>
       </c>
       <c r="R6" t="n">
-        <v>6663471</v>
+        <v>6663507</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,7 +1270,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1280,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1396,7 +1434,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121379825</v>
+        <v>121379027</v>
       </c>
       <c r="B8" t="n">
         <v>98081</v>
@@ -1436,13 +1474,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536119</v>
+        <v>536126</v>
       </c>
       <c r="R8" t="n">
-        <v>6663816</v>
+        <v>6663835</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,12 +1519,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Snitslat av SKS.</t>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1551,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121378966</v>
+        <v>121379200</v>
       </c>
       <c r="B9" t="n">
-        <v>77537</v>
+        <v>43707</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,41 +1563,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6000248</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536122</v>
+        <v>536184</v>
       </c>
       <c r="R9" t="n">
-        <v>6663736</v>
+        <v>6663844</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1591,7 +1631,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,12 +1641,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,35 +1655,10 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1658,7 +1673,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121379908</v>
+        <v>121379915</v>
       </c>
       <c r="B10" t="n">
         <v>98081</v>
@@ -1692,24 +1707,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535988</v>
+        <v>536016</v>
       </c>
       <c r="R10" t="n">
-        <v>6663825</v>
+        <v>6663828</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1738,7 +1748,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1748,12 +1758,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1790,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121379915</v>
+        <v>121381766</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>74647</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,25 +1802,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1820,10 +1830,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536016</v>
+        <v>536080</v>
       </c>
       <c r="R11" t="n">
-        <v>6663828</v>
+        <v>6663854</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1855,7 +1865,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1865,12 +1875,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,6 +1891,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1897,10 +1922,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121400775</v>
+        <v>121381773</v>
       </c>
       <c r="B12" t="n">
-        <v>77550</v>
+        <v>57720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1909,41 +1934,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003412</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Röd kådsvartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis zebrina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Rikkinen &amp; Tuovila</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536121</v>
+        <v>536080</v>
       </c>
       <c r="R12" t="n">
-        <v>6663736</v>
+        <v>6663854</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1970,17 +2001,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1989,49 +2030,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121379200</v>
+        <v>121380560</v>
       </c>
       <c r="B13" t="n">
-        <v>43707</v>
+        <v>74520</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,42 +2064,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101735</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536184</v>
+        <v>536014</v>
       </c>
       <c r="R13" t="n">
-        <v>6663844</v>
+        <v>6663853</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2108,7 +2123,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2118,12 +2133,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,6 +2149,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2150,10 +2180,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121377312</v>
+        <v>121377259</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>57720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2162,46 +2192,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536183</v>
+        <v>536132</v>
       </c>
       <c r="R14" t="n">
-        <v>6663507</v>
+        <v>6663471</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2230,7 +2255,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2240,12 +2265,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>3 fröställningar.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2272,10 +2292,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121377626</v>
+        <v>121377665</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>56404</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2284,40 +2304,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100045</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2361,7 +2376,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2371,12 +2386,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2403,10 +2413,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121380560</v>
+        <v>121400778</v>
       </c>
       <c r="B16" t="n">
-        <v>74520</v>
+        <v>77537</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2415,41 +2425,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6428</v>
+        <v>6000248</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536014</v>
+        <v>536121</v>
       </c>
       <c r="R16" t="n">
-        <v>6663853</v>
+        <v>6663736</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2473,27 +2486,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2502,40 +2505,46 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>kåda # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121379027</v>
+        <v>121377626</v>
       </c>
       <c r="B17" t="n">
         <v>98081</v>
@@ -2568,20 +2577,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536126</v>
+        <v>536173</v>
       </c>
       <c r="R17" t="n">
-        <v>6663835</v>
+        <v>6663536</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2610,7 +2633,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2620,12 +2643,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2652,10 +2675,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121381766</v>
+        <v>121379825</v>
       </c>
       <c r="B18" t="n">
-        <v>74647</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2664,25 +2687,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2692,10 +2715,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536080</v>
+        <v>536119</v>
       </c>
       <c r="R18" t="n">
-        <v>6663854</v>
+        <v>6663816</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2727,7 +2750,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2737,12 +2760,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,21 +2776,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2784,10 +2792,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121381773</v>
+        <v>121379908</v>
       </c>
       <c r="B19" t="n">
-        <v>57717</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2796,35 +2804,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2833,13 +2837,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536080</v>
+        <v>535988</v>
       </c>
       <c r="R19" t="n">
-        <v>6663854</v>
+        <v>6663825</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2868,7 +2872,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2878,12 +2882,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,17 +2907,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121400778</v>
+        <v>121380829</v>
       </c>
       <c r="B20" t="n">
-        <v>77537</v>
+        <v>90644</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2922,41 +2926,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6000248</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536121</v>
+        <v>536023</v>
       </c>
       <c r="R20" t="n">
-        <v>6663736</v>
+        <v>6663863</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2983,17 +2984,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3002,15 +3008,9 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3023,21 +3023,152 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>kåda # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121379920</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74520</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ungsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>535986</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6663849</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121400775</v>
+        <v>121378966</v>
       </c>
       <c r="B3" t="n">
-        <v>77550</v>
+        <v>77537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003412</v>
+        <v>6000248</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd kådsvartspik</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis zebrina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rikkinen &amp; Tuovila</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536121</v>
+        <v>536122</v>
       </c>
       <c r="R3" t="n">
         <v>6663736</v>
@@ -860,17 +860,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,45 +893,49 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>kåda # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121378966</v>
+        <v>121400775</v>
       </c>
       <c r="B4" t="n">
-        <v>77537</v>
+        <v>77550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +948,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6000248</v>
+        <v>6003412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Röd kådsvartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Chaenothecopsis zebrina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>Rikkinen &amp; Tuovila</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,7 +975,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536122</v>
+        <v>536121</v>
       </c>
       <c r="R4" t="n">
         <v>6663736</v>
@@ -991,27 +1005,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,39 +1028,35 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
+          <t>kåda # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121378966</v>
+        <v>121400775</v>
       </c>
       <c r="B3" t="n">
-        <v>77537</v>
+        <v>77550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6000248</v>
+        <v>6003412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Röd kådsvartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Chaenothecopsis zebrina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>Rikkinen &amp; Tuovila</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536122</v>
+        <v>536121</v>
       </c>
       <c r="R3" t="n">
         <v>6663736</v>
@@ -860,27 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,49 +883,45 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
+          <t>kåda # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121400775</v>
+        <v>121378966</v>
       </c>
       <c r="B4" t="n">
-        <v>77550</v>
+        <v>77537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003412</v>
+        <v>6000248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd kådsvartspik</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis zebrina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rikkinen &amp; Tuovila</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -975,7 +961,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536121</v>
+        <v>536122</v>
       </c>
       <c r="R4" t="n">
         <v>6663736</v>
@@ -1005,17 +991,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,35 +1024,39 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>kåda # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -918,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121378966</v>
+        <v>121400778</v>
       </c>
       <c r="B4" t="n">
         <v>77537</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536122</v>
+        <v>536121</v>
       </c>
       <c r="R4" t="n">
         <v>6663736</v>
@@ -991,27 +991,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,49 +1014,45 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
+          <t>kåda # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121381688</v>
+        <v>121379915</v>
       </c>
       <c r="B5" t="n">
-        <v>90662</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,25 +1061,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1103,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536047</v>
+        <v>536016</v>
       </c>
       <c r="R5" t="n">
-        <v>6663867</v>
+        <v>6663828</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1138,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1134,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,21 +1150,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1190,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121377312</v>
+        <v>121381766</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>74647</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,46 +1178,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536183</v>
+        <v>536080</v>
       </c>
       <c r="R6" t="n">
-        <v>6663507</v>
+        <v>6663854</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1280,12 +1251,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3 fröställningar.</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,6 +1267,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1312,10 +1298,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121381754</v>
+        <v>121379027</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1324,43 +1310,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536061</v>
+        <v>536126</v>
       </c>
       <c r="R7" t="n">
-        <v>6663870</v>
+        <v>6663835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,7 +1373,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,12 +1383,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,7 +1415,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121379027</v>
+        <v>121379825</v>
       </c>
       <c r="B8" t="n">
         <v>98081</v>
@@ -1474,13 +1455,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536126</v>
+        <v>536119</v>
       </c>
       <c r="R8" t="n">
-        <v>6663835</v>
+        <v>6663816</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1490,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,12 +1500,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1551,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121379200</v>
+        <v>121380829</v>
       </c>
       <c r="B9" t="n">
-        <v>43707</v>
+        <v>90644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1563,43 +1544,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536184</v>
+        <v>536023</v>
       </c>
       <c r="R9" t="n">
-        <v>6663844</v>
+        <v>6663863</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1631,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1641,12 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,6 +1628,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1673,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121379915</v>
+        <v>121379200</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>43707</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,38 +1671,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536016</v>
+        <v>536184</v>
       </c>
       <c r="R10" t="n">
-        <v>6663828</v>
+        <v>6663844</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1748,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1758,12 +1749,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121381766</v>
+        <v>121377312</v>
       </c>
       <c r="B11" t="n">
-        <v>74647</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1802,41 +1793,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536080</v>
+        <v>536183</v>
       </c>
       <c r="R11" t="n">
-        <v>6663854</v>
+        <v>6663507</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1865,7 +1861,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1875,12 +1871,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1891,21 +1887,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1922,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121381773</v>
+        <v>121379908</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,35 +1915,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1971,13 +1948,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536080</v>
+        <v>535988</v>
       </c>
       <c r="R12" t="n">
-        <v>6663854</v>
+        <v>6663825</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2006,7 +1983,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2016,12 +1993,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2041,17 +2018,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121380560</v>
+        <v>121377259</v>
       </c>
       <c r="B13" t="n">
-        <v>74520</v>
+        <v>57720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2064,21 +2041,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2088,13 +2065,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536014</v>
+        <v>536132</v>
       </c>
       <c r="R13" t="n">
-        <v>6663853</v>
+        <v>6663471</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2123,7 +2100,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2133,12 +2110,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2149,21 +2121,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2180,10 +2137,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121377259</v>
+        <v>121378966</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>77537</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2192,38 +2149,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>6000248</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536132</v>
+        <v>536122</v>
       </c>
       <c r="R14" t="n">
-        <v>6663471</v>
+        <v>6663736</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2255,7 +2215,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2265,7 +2225,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2274,10 +2239,35 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AT14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW14" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -2292,10 +2282,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121377665</v>
+        <v>121381773</v>
       </c>
       <c r="B15" t="n">
-        <v>56404</v>
+        <v>57720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2308,16 +2298,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100045</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2327,12 +2317,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2341,10 +2331,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536173</v>
+        <v>536080</v>
       </c>
       <c r="R15" t="n">
-        <v>6663536</v>
+        <v>6663854</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2376,7 +2366,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2386,7 +2376,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2406,17 +2401,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121400778</v>
+        <v>121377665</v>
       </c>
       <c r="B16" t="n">
-        <v>77537</v>
+        <v>56404</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2425,41 +2420,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6000248</v>
+        <v>100045</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536121</v>
+        <v>536173</v>
       </c>
       <c r="R16" t="n">
-        <v>6663736</v>
+        <v>6663536</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2486,17 +2487,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2505,49 +2511,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121377626</v>
+        <v>121380560</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>74520</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2556,55 +2541,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536173</v>
+        <v>536014</v>
       </c>
       <c r="R17" t="n">
-        <v>6663536</v>
+        <v>6663853</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2633,7 +2604,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2643,12 +2614,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2659,6 +2630,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2675,10 +2661,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121379825</v>
+        <v>121381688</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>90662</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2687,25 +2673,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2715,10 +2701,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536119</v>
+        <v>536047</v>
       </c>
       <c r="R18" t="n">
-        <v>6663816</v>
+        <v>6663867</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2750,7 +2736,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2760,12 +2746,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Snitslat av SKS.</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2776,6 +2757,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2792,7 +2788,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121379908</v>
+        <v>121377626</v>
       </c>
       <c r="B19" t="n">
         <v>98081</v>
@@ -2825,7 +2821,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2837,13 +2842,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535988</v>
+        <v>536173</v>
       </c>
       <c r="R19" t="n">
-        <v>6663825</v>
+        <v>6663536</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2872,7 +2877,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2882,12 +2887,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2914,10 +2919,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121380829</v>
+        <v>121381754</v>
       </c>
       <c r="B20" t="n">
-        <v>90644</v>
+        <v>5169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2926,41 +2931,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536023</v>
+        <v>536061</v>
       </c>
       <c r="R20" t="n">
-        <v>6663863</v>
+        <v>6663870</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2989,7 +2999,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2999,7 +3009,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3010,21 +3025,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121400775</v>
+        <v>121381754</v>
       </c>
       <c r="B3" t="n">
-        <v>77550</v>
+        <v>5169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,44 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003412</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd kådsvartspik</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis zebrina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rikkinen &amp; Tuovila</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536121</v>
+        <v>536061</v>
       </c>
       <c r="R3" t="n">
-        <v>6663736</v>
+        <v>6663870</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +862,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,49 +891,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121400778</v>
+        <v>121379915</v>
       </c>
       <c r="B4" t="n">
-        <v>77537</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,41 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6000248</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536121</v>
+        <v>536016</v>
       </c>
       <c r="R4" t="n">
-        <v>6663736</v>
+        <v>6663828</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,17 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,49 +1008,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121379915</v>
+        <v>121400775</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>77553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,38 +1038,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6003412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Röd kådsvartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis zebrina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Rikkinen &amp; Tuovila</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536016</v>
+        <v>536121</v>
       </c>
       <c r="R5" t="n">
-        <v>6663828</v>
+        <v>6663736</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,27 +1099,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,28 +1118,49 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121381766</v>
+        <v>121379027</v>
       </c>
       <c r="B6" t="n">
-        <v>74647</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,25 +1169,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1206,13 +1197,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536080</v>
+        <v>536126</v>
       </c>
       <c r="R6" t="n">
-        <v>6663854</v>
+        <v>6663835</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,12 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,21 +1258,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1298,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121379027</v>
+        <v>121379908</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,16 +1308,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536126</v>
+        <v>535988</v>
       </c>
       <c r="R7" t="n">
-        <v>6663835</v>
+        <v>6663825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1383,12 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121379825</v>
+        <v>121381766</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>74649</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,25 +1408,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1455,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536119</v>
+        <v>536080</v>
       </c>
       <c r="R8" t="n">
-        <v>6663816</v>
+        <v>6663854</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1490,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,12 +1481,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Snitslat av SKS.</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,6 +1497,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1532,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121380829</v>
+        <v>121381773</v>
       </c>
       <c r="B9" t="n">
-        <v>90644</v>
+        <v>57720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1544,38 +1540,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536023</v>
+        <v>536080</v>
       </c>
       <c r="R9" t="n">
-        <v>6663863</v>
+        <v>6663854</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1607,7 +1612,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1622,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,21 +1638,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1652,17 +1647,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121379200</v>
+        <v>121378966</v>
       </c>
       <c r="B10" t="n">
-        <v>43707</v>
+        <v>77540</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,43 +1666,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101735</v>
+        <v>6000248</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536184</v>
+        <v>536122</v>
       </c>
       <c r="R10" t="n">
-        <v>6663844</v>
+        <v>6663736</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1739,7 +1732,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,12 +1742,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,10 +1756,35 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW10" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1781,10 +1799,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121377312</v>
+        <v>121380560</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>74522</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1793,46 +1811,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536183</v>
+        <v>536014</v>
       </c>
       <c r="R11" t="n">
-        <v>6663507</v>
+        <v>6663853</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,7 +1874,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1871,12 +1884,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>3 fröställningar.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,6 +1900,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1903,10 +1931,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121379908</v>
+        <v>121377626</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1936,7 +1964,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1948,13 +1985,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535988</v>
+        <v>536173</v>
       </c>
       <c r="R12" t="n">
-        <v>6663825</v>
+        <v>6663536</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1983,7 +2020,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1993,12 +2030,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2137,10 +2174,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121378966</v>
+        <v>121377665</v>
       </c>
       <c r="B14" t="n">
-        <v>77537</v>
+        <v>56404</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,41 +2186,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6000248</v>
+        <v>100045</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536122</v>
+        <v>536173</v>
       </c>
       <c r="R14" t="n">
-        <v>6663736</v>
+        <v>6663536</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2215,7 +2258,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2225,12 +2268,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2239,35 +2277,10 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -2282,10 +2295,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121381773</v>
+        <v>121379825</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2294,47 +2307,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536080</v>
+        <v>536119</v>
       </c>
       <c r="R15" t="n">
-        <v>6663854</v>
+        <v>6663816</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2366,7 +2370,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2376,12 +2380,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2401,17 +2405,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121377665</v>
+        <v>121381688</v>
       </c>
       <c r="B16" t="n">
-        <v>56404</v>
+        <v>90674</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2424,43 +2428,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100045</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536173</v>
+        <v>536047</v>
       </c>
       <c r="R16" t="n">
-        <v>6663536</v>
+        <v>6663867</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2492,7 +2487,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2502,7 +2497,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2513,6 +2508,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2529,10 +2539,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121380560</v>
+        <v>121377312</v>
       </c>
       <c r="B17" t="n">
-        <v>74520</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2541,41 +2551,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536014</v>
+        <v>536183</v>
       </c>
       <c r="R17" t="n">
-        <v>6663853</v>
+        <v>6663507</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2604,7 +2619,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2614,12 +2629,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2630,21 +2645,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2661,10 +2661,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121381688</v>
+        <v>121400778</v>
       </c>
       <c r="B18" t="n">
-        <v>90662</v>
+        <v>77540</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2673,38 +2673,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6000248</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536047</v>
+        <v>536121</v>
       </c>
       <c r="R18" t="n">
-        <v>6663867</v>
+        <v>6663736</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2731,22 +2734,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,9 +2753,15 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2770,28 +2774,28 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kåda # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121377626</v>
+        <v>121380829</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>90656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2800,52 +2804,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536173</v>
+        <v>536023</v>
       </c>
       <c r="R19" t="n">
-        <v>6663536</v>
+        <v>6663863</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2877,7 +2867,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2887,12 +2877,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,6 +2888,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121381754</v>
+        <v>121379200</v>
       </c>
       <c r="B20" t="n">
-        <v>5169</v>
+        <v>43707</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2935,27 +2935,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536061</v>
+        <v>536184</v>
       </c>
       <c r="R20" t="n">
-        <v>6663870</v>
+        <v>6663844</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3044,7 +3044,7 @@
         <v>121379920</v>
       </c>
       <c r="B21" t="n">
-        <v>74520</v>
+        <v>74522</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121381754</v>
+        <v>121400778</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>77540</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +799,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6000248</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536061</v>
+        <v>536121</v>
       </c>
       <c r="R3" t="n">
-        <v>6663870</v>
+        <v>6663736</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,28 +879,49 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121379915</v>
+        <v>121381754</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +930,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536016</v>
+        <v>536061</v>
       </c>
       <c r="R4" t="n">
-        <v>6663828</v>
+        <v>6663870</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1157,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121379027</v>
+        <v>121378966</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>77540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,41 +1183,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6000248</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536126</v>
+        <v>536122</v>
       </c>
       <c r="R6" t="n">
-        <v>6663835</v>
+        <v>6663736</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1259,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1273,35 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1274,10 +1316,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121379908</v>
+        <v>121380829</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>90657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,46 +1328,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535988</v>
+        <v>536023</v>
       </c>
       <c r="R7" t="n">
-        <v>6663825</v>
+        <v>6663863</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,12 +1401,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,6 +1412,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1396,10 +1443,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121381766</v>
+        <v>121379915</v>
       </c>
       <c r="B8" t="n">
-        <v>74649</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,25 +1455,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1436,10 +1483,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536080</v>
+        <v>536016</v>
       </c>
       <c r="R8" t="n">
-        <v>6663854</v>
+        <v>6663828</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,7 +1518,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,12 +1528,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,21 +1544,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1528,10 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121381773</v>
+        <v>121379027</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,50 +1572,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536080</v>
+        <v>536126</v>
       </c>
       <c r="R9" t="n">
-        <v>6663854</v>
+        <v>6663835</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1612,7 +1635,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1622,12 +1645,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,17 +1670,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121378966</v>
+        <v>121377312</v>
       </c>
       <c r="B10" t="n">
-        <v>77540</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,44 +1689,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6000248</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536122</v>
+        <v>536183</v>
       </c>
       <c r="R10" t="n">
-        <v>6663736</v>
+        <v>6663507</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1732,7 +1757,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1742,12 +1767,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,35 +1781,10 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121380560</v>
+        <v>121379825</v>
       </c>
       <c r="B11" t="n">
-        <v>74522</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1811,25 +1811,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1839,13 +1839,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536014</v>
+        <v>536119</v>
       </c>
       <c r="R11" t="n">
-        <v>6663853</v>
+        <v>6663816</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,21 +1900,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1931,10 +1916,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121377626</v>
+        <v>121377665</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>56404</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1943,40 +1928,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100045</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2020,7 +2000,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2030,12 +2010,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2062,10 +2037,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121377259</v>
+        <v>121381766</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>74649</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2078,21 +2053,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2102,10 +2077,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536132</v>
+        <v>536080</v>
       </c>
       <c r="R13" t="n">
-        <v>6663471</v>
+        <v>6663854</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2137,7 +2112,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2147,7 +2122,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,6 +2138,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2174,10 +2169,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121377665</v>
+        <v>121381688</v>
       </c>
       <c r="B14" t="n">
-        <v>56404</v>
+        <v>90675</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2190,43 +2185,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100045</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536173</v>
+        <v>536047</v>
       </c>
       <c r="R14" t="n">
-        <v>6663536</v>
+        <v>6663867</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2258,7 +2244,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2268,7 +2254,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2279,6 +2265,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2295,10 +2296,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121379825</v>
+        <v>121380560</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>74522</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2307,25 +2308,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2335,13 +2336,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536119</v>
+        <v>536014</v>
       </c>
       <c r="R15" t="n">
-        <v>6663816</v>
+        <v>6663853</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2370,7 +2371,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2380,12 +2381,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Snitslat av SKS.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2396,6 +2397,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2412,10 +2428,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121381688</v>
+        <v>121377626</v>
       </c>
       <c r="B16" t="n">
-        <v>90674</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2424,38 +2440,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536047</v>
+        <v>536173</v>
       </c>
       <c r="R16" t="n">
-        <v>6663867</v>
+        <v>6663536</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2487,7 +2517,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2497,7 +2527,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,21 +2543,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2539,10 +2559,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121377312</v>
+        <v>121377259</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>57720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2551,46 +2571,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536183</v>
+        <v>536132</v>
       </c>
       <c r="R17" t="n">
-        <v>6663507</v>
+        <v>6663471</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2619,7 +2634,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2629,12 +2644,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>3 fröställningar.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2661,10 +2671,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121400778</v>
+        <v>121381773</v>
       </c>
       <c r="B18" t="n">
-        <v>77540</v>
+        <v>57720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2673,41 +2683,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6000248</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536121</v>
+        <v>536080</v>
       </c>
       <c r="R18" t="n">
-        <v>6663736</v>
+        <v>6663854</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2734,17 +2750,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,49 +2779,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121380829</v>
+        <v>121379908</v>
       </c>
       <c r="B19" t="n">
-        <v>90656</v>
+        <v>98095</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2804,41 +2809,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536023</v>
+        <v>535988</v>
       </c>
       <c r="R19" t="n">
-        <v>6663863</v>
+        <v>6663825</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2867,7 +2877,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2877,7 +2887,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2888,21 +2903,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121400778</v>
+        <v>121378966</v>
       </c>
       <c r="B3" t="n">
-        <v>77540</v>
+        <v>77543</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536121</v>
+        <v>536122</v>
       </c>
       <c r="R3" t="n">
         <v>6663736</v>
@@ -860,17 +860,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,45 +893,49 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>kåda # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121381754</v>
+        <v>121379200</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>43710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,27 +948,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536061</v>
+        <v>536184</v>
       </c>
       <c r="R4" t="n">
-        <v>6663870</v>
+        <v>6663844</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1022,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121400775</v>
+        <v>121381754</v>
       </c>
       <c r="B5" t="n">
-        <v>77553</v>
+        <v>5172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,44 +1066,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003412</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Röd kådsvartspik</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis zebrina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Rikkinen &amp; Tuovila</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536121</v>
+        <v>536061</v>
       </c>
       <c r="R5" t="n">
-        <v>6663736</v>
+        <v>6663870</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,17 +1129,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,49 +1158,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121378966</v>
+        <v>121379915</v>
       </c>
       <c r="B6" t="n">
-        <v>77540</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,41 +1188,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6000248</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536122</v>
+        <v>536016</v>
       </c>
       <c r="R6" t="n">
-        <v>6663736</v>
+        <v>6663828</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1249,7 +1251,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,12 +1261,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,35 +1275,10 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1316,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121380829</v>
+        <v>121381766</v>
       </c>
       <c r="B7" t="n">
-        <v>90657</v>
+        <v>74652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1328,25 +1305,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1356,10 +1333,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536023</v>
+        <v>536080</v>
       </c>
       <c r="R7" t="n">
-        <v>6663863</v>
+        <v>6663854</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1391,7 +1368,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1401,7 +1378,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121379915</v>
+        <v>121377626</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,17 +1458,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536016</v>
+        <v>536173</v>
       </c>
       <c r="R8" t="n">
-        <v>6663828</v>
+        <v>6663536</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1518,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1528,12 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,10 +1556,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121379027</v>
+        <v>121379825</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1600,13 +1596,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536126</v>
+        <v>536119</v>
       </c>
       <c r="R9" t="n">
-        <v>6663835</v>
+        <v>6663816</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1635,7 +1631,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1645,12 +1641,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121377312</v>
+        <v>121400778</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>77543</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,46 +1685,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6000248</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536183</v>
+        <v>536121</v>
       </c>
       <c r="R10" t="n">
-        <v>6663507</v>
+        <v>6663736</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1752,27 +1746,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3 fröställningar.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,28 +1765,49 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121379825</v>
+        <v>121379908</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,19 +1838,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536119</v>
+        <v>535988</v>
       </c>
       <c r="R11" t="n">
-        <v>6663816</v>
+        <v>6663825</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1874,7 +1884,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1884,12 +1894,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Snitslat av SKS.</t>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,10 +1926,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121377665</v>
+        <v>121381688</v>
       </c>
       <c r="B12" t="n">
-        <v>56404</v>
+        <v>90678</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1932,43 +1942,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100045</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536173</v>
+        <v>536047</v>
       </c>
       <c r="R12" t="n">
-        <v>6663536</v>
+        <v>6663867</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2000,7 +2001,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2010,7 +2011,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,6 +2022,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2037,10 +2053,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121381766</v>
+        <v>121377665</v>
       </c>
       <c r="B13" t="n">
-        <v>74649</v>
+        <v>56407</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2053,34 +2069,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>100045</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536080</v>
+        <v>536173</v>
       </c>
       <c r="R13" t="n">
-        <v>6663854</v>
+        <v>6663536</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2112,7 +2137,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2122,12 +2147,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På död gran.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2138,21 +2158,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2169,10 +2174,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121381688</v>
+        <v>121377259</v>
       </c>
       <c r="B14" t="n">
-        <v>90675</v>
+        <v>57723</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2185,21 +2190,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2209,10 +2214,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536047</v>
+        <v>536132</v>
       </c>
       <c r="R14" t="n">
-        <v>6663867</v>
+        <v>6663471</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2244,7 +2249,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2254,7 +2259,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2265,21 +2270,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2296,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121380560</v>
+        <v>121400775</v>
       </c>
       <c r="B15" t="n">
-        <v>74522</v>
+        <v>77556</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2308,41 +2298,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6428</v>
+        <v>6003412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Röd kådsvartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis zebrina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Rikkinen &amp; Tuovila</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536014</v>
+        <v>536121</v>
       </c>
       <c r="R15" t="n">
-        <v>6663853</v>
+        <v>6663736</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2366,27 +2359,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,43 +2378,49 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>kåda # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121377626</v>
+        <v>121379027</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2461,34 +2450,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536173</v>
+        <v>536126</v>
       </c>
       <c r="R16" t="n">
-        <v>6663536</v>
+        <v>6663835</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2517,7 +2492,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2527,12 +2502,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2559,10 +2534,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121377259</v>
+        <v>121381773</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2592,17 +2567,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536132</v>
+        <v>536080</v>
       </c>
       <c r="R17" t="n">
-        <v>6663471</v>
+        <v>6663854</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2634,7 +2618,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2644,7 +2628,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2664,17 +2653,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121381773</v>
+        <v>121380560</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>74525</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2687,46 +2676,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536080</v>
+        <v>536014</v>
       </c>
       <c r="R18" t="n">
-        <v>6663854</v>
+        <v>6663853</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2755,7 +2735,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2765,12 +2745,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2781,6 +2761,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2790,17 +2785,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121379908</v>
+        <v>121380829</v>
       </c>
       <c r="B19" t="n">
-        <v>98095</v>
+        <v>90660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2809,46 +2804,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535988</v>
+        <v>536023</v>
       </c>
       <c r="R19" t="n">
-        <v>6663825</v>
+        <v>6663863</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2877,7 +2867,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2887,12 +2877,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,6 +2888,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121379200</v>
+        <v>121377312</v>
       </c>
       <c r="B20" t="n">
-        <v>43707</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2931,31 +2931,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536184</v>
+        <v>536183</v>
       </c>
       <c r="R20" t="n">
-        <v>6663844</v>
+        <v>6663507</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3044,7 +3044,7 @@
         <v>121379920</v>
       </c>
       <c r="B21" t="n">
-        <v>74522</v>
+        <v>74525</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121378966</v>
+        <v>121379825</v>
       </c>
       <c r="B3" t="n">
-        <v>77543</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6000248</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536122</v>
+        <v>536119</v>
       </c>
       <c r="R3" t="n">
-        <v>6663736</v>
+        <v>6663816</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,35 +886,10 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -932,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121379200</v>
+        <v>121400778</v>
       </c>
       <c r="B4" t="n">
-        <v>43710</v>
+        <v>77543</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,43 +916,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101735</v>
+        <v>6000248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536184</v>
+        <v>536121</v>
       </c>
       <c r="R4" t="n">
-        <v>6663844</v>
+        <v>6663736</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,27 +977,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,28 +996,49 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121381754</v>
+        <v>121379915</v>
       </c>
       <c r="B5" t="n">
-        <v>5172</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,46 +1047,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536061</v>
+        <v>536016</v>
       </c>
       <c r="R5" t="n">
-        <v>6663870</v>
+        <v>6663828</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121379915</v>
+        <v>121381766</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>74652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,25 +1164,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1216,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536016</v>
+        <v>536080</v>
       </c>
       <c r="R6" t="n">
-        <v>6663828</v>
+        <v>6663854</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1261,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,6 +1253,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1293,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121381766</v>
+        <v>121380560</v>
       </c>
       <c r="B7" t="n">
-        <v>74652</v>
+        <v>74525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,21 +1300,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,13 +1324,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536080</v>
+        <v>536014</v>
       </c>
       <c r="R7" t="n">
-        <v>6663854</v>
+        <v>6663853</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1378,12 +1369,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,17 +1388,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1425,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121377626</v>
+        <v>121381754</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>5172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,40 +1428,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1479,13 +1461,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536173</v>
+        <v>536061</v>
       </c>
       <c r="R8" t="n">
-        <v>6663536</v>
+        <v>6663870</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1514,7 +1496,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,12 +1506,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121379825</v>
+        <v>121381773</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>57723</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1568,38 +1550,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536119</v>
+        <v>536080</v>
       </c>
       <c r="R9" t="n">
-        <v>6663816</v>
+        <v>6663854</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1631,7 +1622,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1641,12 +1632,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Snitslat av SKS.</t>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,14 +1657,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121400778</v>
+        <v>121378966</v>
       </c>
       <c r="B10" t="n">
         <v>77543</v>
@@ -1716,7 +1707,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536121</v>
+        <v>536122</v>
       </c>
       <c r="R10" t="n">
         <v>6663736</v>
@@ -1746,17 +1737,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,35 +1770,39 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>kåda # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1926,10 +1931,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121381688</v>
+        <v>121380829</v>
       </c>
       <c r="B12" t="n">
-        <v>90678</v>
+        <v>90660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1938,25 +1943,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1966,10 +1971,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536047</v>
+        <v>536023</v>
       </c>
       <c r="R12" t="n">
-        <v>6663867</v>
+        <v>6663863</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2001,7 +2006,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2011,7 +2016,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121377665</v>
+        <v>121381688</v>
       </c>
       <c r="B13" t="n">
-        <v>56407</v>
+        <v>90678</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2069,43 +2074,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100045</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536173</v>
+        <v>536047</v>
       </c>
       <c r="R13" t="n">
-        <v>6663536</v>
+        <v>6663867</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2137,7 +2133,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2147,7 +2143,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,6 +2154,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2174,10 +2185,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121377259</v>
+        <v>121379027</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2186,25 +2197,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2214,13 +2225,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536132</v>
+        <v>536126</v>
       </c>
       <c r="R14" t="n">
-        <v>6663471</v>
+        <v>6663835</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2249,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2259,7 +2270,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2417,7 +2433,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121379027</v>
+        <v>121377626</v>
       </c>
       <c r="B16" t="n">
         <v>98098</v>
@@ -2450,20 +2466,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536126</v>
+        <v>536173</v>
       </c>
       <c r="R16" t="n">
-        <v>6663835</v>
+        <v>6663536</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2492,7 +2522,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2502,12 +2532,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2534,10 +2564,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121381773</v>
+        <v>121377312</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2546,35 +2576,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2583,13 +2609,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536080</v>
+        <v>536183</v>
       </c>
       <c r="R17" t="n">
-        <v>6663854</v>
+        <v>6663507</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2618,7 +2644,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2628,12 +2654,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2653,17 +2679,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121380560</v>
+        <v>121377665</v>
       </c>
       <c r="B18" t="n">
-        <v>74525</v>
+        <v>56407</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2676,37 +2702,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6428</v>
+        <v>100045</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536014</v>
+        <v>536173</v>
       </c>
       <c r="R18" t="n">
-        <v>6663853</v>
+        <v>6663536</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2735,7 +2770,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2745,12 +2780,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2761,21 +2791,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2792,10 +2807,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121380829</v>
+        <v>121377259</v>
       </c>
       <c r="B19" t="n">
-        <v>90660</v>
+        <v>57723</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2804,25 +2819,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2832,10 +2847,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536023</v>
+        <v>536132</v>
       </c>
       <c r="R19" t="n">
-        <v>6663863</v>
+        <v>6663471</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2867,7 +2882,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2877,7 +2892,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2888,21 +2903,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121377312</v>
+        <v>121379920</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>74525</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2931,46 +2931,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536183</v>
+        <v>535986</v>
       </c>
       <c r="R20" t="n">
-        <v>6663507</v>
+        <v>6663849</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2999,7 +2997,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3009,12 +3007,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>3 fröställningar.</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3023,8 +3016,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3041,10 +3050,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121379920</v>
+        <v>121379200</v>
       </c>
       <c r="B21" t="n">
-        <v>74525</v>
+        <v>43710</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3057,40 +3066,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6428</v>
+        <v>101735</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535986</v>
+        <v>536184</v>
       </c>
       <c r="R21" t="n">
-        <v>6663849</v>
+        <v>6663844</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3119,7 +3130,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3129,7 +3140,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3138,24 +3154,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121381688</v>
+        <v>121379027</v>
       </c>
       <c r="B13" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536047</v>
+        <v>536126</v>
       </c>
       <c r="R13" t="n">
-        <v>6663867</v>
+        <v>6663835</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2143,7 +2143,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2154,21 +2159,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2185,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121379027</v>
+        <v>121381688</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2197,25 +2187,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2225,13 +2215,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536126</v>
+        <v>536047</v>
       </c>
       <c r="R14" t="n">
-        <v>6663835</v>
+        <v>6663867</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2260,7 +2250,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,12 +2260,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2286,6 +2271,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121379915</v>
+        <v>121381766</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>74652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,25 +1047,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536016</v>
+        <v>536080</v>
       </c>
       <c r="R5" t="n">
-        <v>6663828</v>
+        <v>6663854</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,6 +1136,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1152,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121381766</v>
+        <v>121379915</v>
       </c>
       <c r="B6" t="n">
-        <v>74652</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,25 +1179,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1192,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536080</v>
+        <v>536016</v>
       </c>
       <c r="R6" t="n">
-        <v>6663854</v>
+        <v>6663828</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1252,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,21 +1268,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -2058,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121379027</v>
+        <v>121381688</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536126</v>
+        <v>536047</v>
       </c>
       <c r="R13" t="n">
-        <v>6663835</v>
+        <v>6663867</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2143,12 +2143,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,6 +2154,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2175,10 +2185,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121381688</v>
+        <v>121379027</v>
       </c>
       <c r="B14" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,25 +2197,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2215,13 +2225,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536047</v>
+        <v>536126</v>
       </c>
       <c r="R14" t="n">
-        <v>6663867</v>
+        <v>6663835</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2250,7 +2260,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2260,7 +2270,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2271,21 +2286,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121379825</v>
+        <v>121379908</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,19 +821,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536119</v>
+        <v>535988</v>
       </c>
       <c r="R3" t="n">
-        <v>6663816</v>
+        <v>6663825</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Snitslat av SKS.</t>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121400778</v>
+        <v>121381766</v>
       </c>
       <c r="B4" t="n">
-        <v>77543</v>
+        <v>74653</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6000248</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536121</v>
+        <v>536080</v>
       </c>
       <c r="R4" t="n">
-        <v>6663736</v>
+        <v>6663854</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,17 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +1008,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1017,28 +1023,28 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>kåda # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121381766</v>
+        <v>121381688</v>
       </c>
       <c r="B5" t="n">
-        <v>74652</v>
+        <v>90684</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536080</v>
+        <v>536047</v>
       </c>
       <c r="R5" t="n">
-        <v>6663854</v>
+        <v>6663867</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På död gran.</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,7 +1171,7 @@
         <v>121379915</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1284,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121380560</v>
+        <v>121378966</v>
       </c>
       <c r="B7" t="n">
-        <v>74525</v>
+        <v>77544</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,41 +1297,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>6000248</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536014</v>
+        <v>536122</v>
       </c>
       <c r="R7" t="n">
-        <v>6663853</v>
+        <v>6663736</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,12 +1373,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,25 +1387,35 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1416,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121381754</v>
+        <v>121377312</v>
       </c>
       <c r="B8" t="n">
-        <v>5172</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,31 +1442,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1461,13 +1475,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536061</v>
+        <v>536183</v>
       </c>
       <c r="R8" t="n">
-        <v>6663870</v>
+        <v>6663507</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,7 +1510,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1506,12 +1520,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,10 +1552,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121381773</v>
+        <v>121381754</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>5172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,31 +1568,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1587,13 +1597,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536080</v>
+        <v>536061</v>
       </c>
       <c r="R9" t="n">
-        <v>6663854</v>
+        <v>6663870</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1622,7 +1632,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1632,12 +1642,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,17 +1667,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121378966</v>
+        <v>121377665</v>
       </c>
       <c r="B10" t="n">
-        <v>77543</v>
+        <v>56408</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,41 +1686,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6000248</v>
+        <v>100045</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536122</v>
+        <v>536173</v>
       </c>
       <c r="R10" t="n">
-        <v>6663736</v>
+        <v>6663536</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1742,7 +1758,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1752,12 +1768,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1766,35 +1777,10 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1809,10 +1795,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121379908</v>
+        <v>121400775</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>77557</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,46 +1807,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6003412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Röd kådsvartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis zebrina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Rikkinen &amp; Tuovila</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535988</v>
+        <v>536121</v>
       </c>
       <c r="R11" t="n">
-        <v>6663825</v>
+        <v>6663736</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1884,27 +1868,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1913,28 +1887,49 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121380829</v>
+        <v>121379825</v>
       </c>
       <c r="B12" t="n">
-        <v>90660</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1943,25 +1938,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1971,10 +1966,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536023</v>
+        <v>536119</v>
       </c>
       <c r="R12" t="n">
-        <v>6663863</v>
+        <v>6663816</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2006,7 +2001,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2016,7 +2011,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,21 +2027,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2058,10 +2043,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121381688</v>
+        <v>121380560</v>
       </c>
       <c r="B13" t="n">
-        <v>90678</v>
+        <v>74526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2074,21 +2059,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2098,13 +2083,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536047</v>
+        <v>536014</v>
       </c>
       <c r="R13" t="n">
-        <v>6663867</v>
+        <v>6663853</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2133,7 +2118,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2143,7 +2128,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,17 +2147,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2185,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121379027</v>
+        <v>121377626</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2218,20 +2208,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536126</v>
+        <v>536173</v>
       </c>
       <c r="R14" t="n">
-        <v>6663835</v>
+        <v>6663536</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2260,7 +2264,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2270,12 +2274,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2302,10 +2306,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121400775</v>
+        <v>121400778</v>
       </c>
       <c r="B15" t="n">
-        <v>77556</v>
+        <v>77544</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,21 +2322,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6003412</v>
+        <v>6000248</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Röd kådsvartspik</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis zebrina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Rikkinen &amp; Tuovila</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2385,7 +2389,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2433,10 +2437,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121377626</v>
+        <v>121377259</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>57724</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2445,52 +2449,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536173</v>
+        <v>536132</v>
       </c>
       <c r="R16" t="n">
-        <v>6663536</v>
+        <v>6663471</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2522,7 +2512,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2532,12 +2522,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2564,10 +2549,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121377312</v>
+        <v>121379027</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2598,24 +2583,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536183</v>
+        <v>536126</v>
       </c>
       <c r="R17" t="n">
-        <v>6663507</v>
+        <v>6663835</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2644,7 +2624,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2654,12 +2634,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>3 fröställningar.</t>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2686,10 +2666,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121377665</v>
+        <v>121380829</v>
       </c>
       <c r="B18" t="n">
-        <v>56407</v>
+        <v>90666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2698,47 +2678,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100045</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536173</v>
+        <v>536023</v>
       </c>
       <c r="R18" t="n">
-        <v>6663536</v>
+        <v>6663863</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2770,7 +2741,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2780,7 +2751,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2791,6 +2762,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2807,10 +2793,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121377259</v>
+        <v>121381773</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57724</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2840,17 +2826,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536132</v>
+        <v>536080</v>
       </c>
       <c r="R19" t="n">
-        <v>6663471</v>
+        <v>6663854</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2882,7 +2877,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2892,7 +2887,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
         <v>121379920</v>
       </c>
       <c r="B20" t="n">
-        <v>74525</v>
+        <v>74526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>121379200</v>
       </c>
       <c r="B21" t="n">
-        <v>43710</v>
+        <v>43711</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -2043,10 +2043,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121380560</v>
+        <v>121377626</v>
       </c>
       <c r="B13" t="n">
-        <v>74526</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2055,41 +2055,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536014</v>
+        <v>536173</v>
       </c>
       <c r="R13" t="n">
-        <v>6663853</v>
+        <v>6663536</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2118,7 +2132,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2128,12 +2142,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,21 +2158,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2175,10 +2174,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121377626</v>
+        <v>121400778</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
+        <v>77544</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,52 +2186,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6000248</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536173</v>
+        <v>536121</v>
       </c>
       <c r="R14" t="n">
-        <v>6663536</v>
+        <v>6663736</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2259,27 +2247,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2288,28 +2266,49 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121400778</v>
+        <v>121380560</v>
       </c>
       <c r="B15" t="n">
-        <v>77544</v>
+        <v>74526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2318,44 +2317,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6000248</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536121</v>
+        <v>536014</v>
       </c>
       <c r="R15" t="n">
-        <v>6663736</v>
+        <v>6663853</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2379,17 +2375,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2398,39 +2404,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>kåda # Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121379908</v>
+        <v>121377312</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535988</v>
+        <v>536183</v>
       </c>
       <c r="R3" t="n">
-        <v>6663825</v>
+        <v>6663507</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121381766</v>
+        <v>121377259</v>
       </c>
       <c r="B4" t="n">
-        <v>74653</v>
+        <v>57725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536080</v>
+        <v>536132</v>
       </c>
       <c r="R4" t="n">
-        <v>6663854</v>
+        <v>6663471</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På död gran.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,21 +1005,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1041,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121381688</v>
+        <v>121377626</v>
       </c>
       <c r="B5" t="n">
-        <v>90684</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,38 +1033,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536047</v>
+        <v>536173</v>
       </c>
       <c r="R5" t="n">
-        <v>6663867</v>
+        <v>6663536</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,21 +1136,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1168,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121379915</v>
+        <v>121377665</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>56409</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,38 +1164,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100045</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536016</v>
+        <v>536173</v>
       </c>
       <c r="R6" t="n">
-        <v>6663828</v>
+        <v>6663536</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1243,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121378966</v>
+        <v>121381766</v>
       </c>
       <c r="B7" t="n">
-        <v>77544</v>
+        <v>74654</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,41 +1285,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6000248</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536122</v>
+        <v>536080</v>
       </c>
       <c r="R7" t="n">
-        <v>6663736</v>
+        <v>6663854</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1363,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,12 +1358,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,35 +1372,25 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1430,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121377312</v>
+        <v>121380829</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>90667</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,46 +1417,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536183</v>
+        <v>536023</v>
       </c>
       <c r="R8" t="n">
-        <v>6663507</v>
+        <v>6663863</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1510,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1520,12 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3 fröställningar.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,6 +1501,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1552,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121381754</v>
+        <v>121381773</v>
       </c>
       <c r="B9" t="n">
-        <v>5172</v>
+        <v>57725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1568,27 +1548,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1597,13 +1581,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536061</v>
+        <v>536080</v>
       </c>
       <c r="R9" t="n">
-        <v>6663870</v>
+        <v>6663854</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1632,7 +1616,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1642,12 +1626,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,17 +1651,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121377665</v>
+        <v>121378966</v>
       </c>
       <c r="B10" t="n">
-        <v>56408</v>
+        <v>77545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,47 +1670,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100045</v>
+        <v>6000248</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536173</v>
+        <v>536122</v>
       </c>
       <c r="R10" t="n">
-        <v>6663536</v>
+        <v>6663736</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1758,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1768,7 +1746,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1777,10 +1760,35 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW10" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1795,10 +1803,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121400775</v>
+        <v>121381688</v>
       </c>
       <c r="B11" t="n">
-        <v>77557</v>
+        <v>90685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1807,41 +1815,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003412</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Röd kådsvartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis zebrina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Rikkinen &amp; Tuovila</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536121</v>
+        <v>536047</v>
       </c>
       <c r="R11" t="n">
-        <v>6663736</v>
+        <v>6663867</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1868,17 +1873,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,15 +1897,9 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1908,28 +1912,28 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>kåda # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121379825</v>
+        <v>121400778</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>77545</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1938,38 +1942,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6000248</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536119</v>
+        <v>536121</v>
       </c>
       <c r="R12" t="n">
-        <v>6663816</v>
+        <v>6663736</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1996,27 +2003,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Snitslat av SKS.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,28 +2022,49 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121377626</v>
+        <v>121380560</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>74527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2055,55 +2073,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536173</v>
+        <v>536014</v>
       </c>
       <c r="R13" t="n">
-        <v>6663536</v>
+        <v>6663853</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2132,7 +2136,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2142,12 +2146,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,6 +2162,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2174,10 +2193,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121400778</v>
+        <v>121379908</v>
       </c>
       <c r="B14" t="n">
-        <v>77544</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2186,44 +2205,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6000248</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536121</v>
+        <v>535988</v>
       </c>
       <c r="R14" t="n">
-        <v>6663736</v>
+        <v>6663825</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2247,17 +2268,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,49 +2297,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121380560</v>
+        <v>121379825</v>
       </c>
       <c r="B15" t="n">
-        <v>74526</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2317,25 +2327,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2345,13 +2355,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536014</v>
+        <v>536119</v>
       </c>
       <c r="R15" t="n">
-        <v>6663853</v>
+        <v>6663816</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2380,7 +2390,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2390,12 +2400,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2406,21 +2416,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2437,10 +2432,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121377259</v>
+        <v>121379915</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2449,25 +2444,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2477,10 +2472,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536132</v>
+        <v>536016</v>
       </c>
       <c r="R16" t="n">
-        <v>6663471</v>
+        <v>6663828</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2512,7 +2507,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2522,7 +2517,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2552,7 +2552,7 @@
         <v>121379027</v>
       </c>
       <c r="B17" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121380829</v>
+        <v>121381754</v>
       </c>
       <c r="B18" t="n">
-        <v>90666</v>
+        <v>5172</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2678,41 +2678,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536023</v>
+        <v>536061</v>
       </c>
       <c r="R18" t="n">
-        <v>6663863</v>
+        <v>6663870</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2741,7 +2746,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2751,7 +2756,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2762,21 +2772,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2793,10 +2788,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121381773</v>
+        <v>121400775</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>77558</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2805,47 +2800,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>6003412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Röd kådsvartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis zebrina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Rikkinen &amp; Tuovila</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536080</v>
+        <v>536121</v>
       </c>
       <c r="R19" t="n">
-        <v>6663854</v>
+        <v>6663736</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2872,27 +2861,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2901,18 +2880,39 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
         <v>121379920</v>
       </c>
       <c r="B20" t="n">
-        <v>74526</v>
+        <v>74527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121377312</v>
+        <v>121379915</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -821,24 +821,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536183</v>
+        <v>536016</v>
       </c>
       <c r="R3" t="n">
-        <v>6663507</v>
+        <v>6663828</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3 fröställningar.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121377259</v>
+        <v>121381766</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>74654</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536132</v>
+        <v>536080</v>
       </c>
       <c r="R4" t="n">
-        <v>6663471</v>
+        <v>6663854</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +1005,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121377626</v>
+        <v>121381688</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,52 +1048,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536173</v>
+        <v>536047</v>
       </c>
       <c r="R5" t="n">
-        <v>6663536</v>
+        <v>6663867</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,6 +1132,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1152,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121377665</v>
+        <v>121379908</v>
       </c>
       <c r="B6" t="n">
-        <v>56409</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,35 +1175,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100045</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1201,13 +1208,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536173</v>
+        <v>535988</v>
       </c>
       <c r="R6" t="n">
-        <v>6663536</v>
+        <v>6663825</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121381766</v>
+        <v>121379825</v>
       </c>
       <c r="B7" t="n">
-        <v>74654</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,25 +1297,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536080</v>
+        <v>536119</v>
       </c>
       <c r="R7" t="n">
-        <v>6663854</v>
+        <v>6663816</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,12 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,21 +1386,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121380829</v>
+        <v>121400778</v>
       </c>
       <c r="B8" t="n">
-        <v>90667</v>
+        <v>77545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,38 +1414,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>6000248</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536023</v>
+        <v>536121</v>
       </c>
       <c r="R8" t="n">
-        <v>6663863</v>
+        <v>6663736</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,22 +1475,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,9 +1494,15 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1514,28 +1515,28 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>kåda # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121381773</v>
+        <v>121380560</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>74527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,46 +1549,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536080</v>
+        <v>536014</v>
       </c>
       <c r="R9" t="n">
-        <v>6663854</v>
+        <v>6663853</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1616,7 +1608,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1626,12 +1618,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,6 +1634,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1651,17 +1658,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121378966</v>
+        <v>121381773</v>
       </c>
       <c r="B10" t="n">
-        <v>77545</v>
+        <v>57725</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1670,41 +1677,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6000248</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536122</v>
+        <v>536080</v>
       </c>
       <c r="R10" t="n">
-        <v>6663736</v>
+        <v>6663854</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1736,7 +1749,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,12 +1759,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,35 +1773,10 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -1796,17 +1784,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121381688</v>
+        <v>121380829</v>
       </c>
       <c r="B11" t="n">
-        <v>90685</v>
+        <v>90667</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1815,25 +1803,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1843,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536047</v>
+        <v>536023</v>
       </c>
       <c r="R11" t="n">
-        <v>6663867</v>
+        <v>6663863</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1878,7 +1866,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1888,7 +1876,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1930,10 +1918,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121400778</v>
+        <v>121377259</v>
       </c>
       <c r="B12" t="n">
-        <v>77545</v>
+        <v>57725</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1942,41 +1930,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6000248</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536121</v>
+        <v>536132</v>
       </c>
       <c r="R12" t="n">
-        <v>6663736</v>
+        <v>6663471</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2003,17 +1988,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2022,49 +2012,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121380560</v>
+        <v>121379027</v>
       </c>
       <c r="B13" t="n">
-        <v>74527</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2073,25 +2042,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2101,10 +2070,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536014</v>
+        <v>536126</v>
       </c>
       <c r="R13" t="n">
-        <v>6663853</v>
+        <v>6663835</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2136,7 +2105,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2146,12 +2115,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,21 +2131,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2193,7 +2147,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121379908</v>
+        <v>121377312</v>
       </c>
       <c r="B14" t="n">
         <v>98105</v>
@@ -2238,13 +2192,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535988</v>
+        <v>536183</v>
       </c>
       <c r="R14" t="n">
-        <v>6663825</v>
+        <v>6663507</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2273,7 +2227,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2283,12 +2237,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2315,10 +2269,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121379825</v>
+        <v>121377665</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>56409</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2327,38 +2281,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100045</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536119</v>
+        <v>536173</v>
       </c>
       <c r="R15" t="n">
-        <v>6663816</v>
+        <v>6663536</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2390,7 +2353,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2400,12 +2363,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Snitslat av SKS.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2432,10 +2390,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121379915</v>
+        <v>121378966</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>77545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2444,38 +2402,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6000248</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536016</v>
+        <v>536122</v>
       </c>
       <c r="R16" t="n">
-        <v>6663828</v>
+        <v>6663736</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2507,7 +2468,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2517,12 +2478,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2531,10 +2492,35 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AT16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW16" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -2549,7 +2535,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121379027</v>
+        <v>121377626</v>
       </c>
       <c r="B17" t="n">
         <v>98105</v>
@@ -2582,20 +2568,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536126</v>
+        <v>536173</v>
       </c>
       <c r="R17" t="n">
-        <v>6663835</v>
+        <v>6663536</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121379915</v>
+        <v>121377626</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -820,17 +820,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536016</v>
+        <v>536173</v>
       </c>
       <c r="R3" t="n">
-        <v>6663828</v>
+        <v>6663536</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121381766</v>
+        <v>121380560</v>
       </c>
       <c r="B4" t="n">
-        <v>74654</v>
+        <v>74527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536080</v>
+        <v>536014</v>
       </c>
       <c r="R4" t="n">
-        <v>6663854</v>
+        <v>6663853</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,17 +1022,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1036,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121381688</v>
+        <v>121381766</v>
       </c>
       <c r="B5" t="n">
-        <v>90685</v>
+        <v>74654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536047</v>
+        <v>536080</v>
       </c>
       <c r="R5" t="n">
-        <v>6663867</v>
+        <v>6663854</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1135,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1182,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121379908</v>
+        <v>121377665</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>56409</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,31 +1194,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100045</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,13 +1231,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535988</v>
+        <v>536173</v>
       </c>
       <c r="R6" t="n">
-        <v>6663825</v>
+        <v>6663536</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1266,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1276,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,7 +1303,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121379825</v>
+        <v>121379027</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1325,13 +1343,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536119</v>
+        <v>536126</v>
       </c>
       <c r="R7" t="n">
-        <v>6663816</v>
+        <v>6663835</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,7 +1378,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1388,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Snitslat av SKS.</t>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1420,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121400778</v>
+        <v>121377259</v>
       </c>
       <c r="B8" t="n">
-        <v>77545</v>
+        <v>57725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,41 +1432,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6000248</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536121</v>
+        <v>536132</v>
       </c>
       <c r="R8" t="n">
-        <v>6663736</v>
+        <v>6663471</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,17 +1490,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,49 +1514,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121380560</v>
+        <v>121381688</v>
       </c>
       <c r="B9" t="n">
-        <v>74527</v>
+        <v>90685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1549,21 +1548,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1573,13 +1572,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536014</v>
+        <v>536047</v>
       </c>
       <c r="R9" t="n">
-        <v>6663853</v>
+        <v>6663867</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1608,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1618,12 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,17 +1631,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1665,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121381773</v>
+        <v>121381754</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>5172</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,31 +1675,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1714,13 +1704,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536080</v>
+        <v>536061</v>
       </c>
       <c r="R10" t="n">
-        <v>6663854</v>
+        <v>6663870</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1749,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1759,12 +1749,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1784,7 +1774,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1918,7 +1908,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121377259</v>
+        <v>121381773</v>
       </c>
       <c r="B12" t="n">
         <v>57725</v>
@@ -1951,17 +1941,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536132</v>
+        <v>536080</v>
       </c>
       <c r="R12" t="n">
-        <v>6663471</v>
+        <v>6663854</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1993,7 +1992,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2003,7 +2002,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,14 +2027,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121379027</v>
+        <v>121379915</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -2070,13 +2074,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536126</v>
+        <v>536016</v>
       </c>
       <c r="R13" t="n">
-        <v>6663835</v>
+        <v>6663828</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2115,12 +2119,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2269,10 +2273,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121377665</v>
+        <v>121379825</v>
       </c>
       <c r="B15" t="n">
-        <v>56409</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2281,47 +2285,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100045</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536173</v>
+        <v>536119</v>
       </c>
       <c r="R15" t="n">
-        <v>6663536</v>
+        <v>6663816</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2353,7 +2348,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2363,7 +2358,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2535,10 +2535,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121377626</v>
+        <v>121400778</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>77545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2547,52 +2547,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6000248</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536173</v>
+        <v>536121</v>
       </c>
       <c r="R17" t="n">
-        <v>6663536</v>
+        <v>6663736</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2619,27 +2608,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2648,28 +2627,49 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121381754</v>
+        <v>121379908</v>
       </c>
       <c r="B18" t="n">
-        <v>5172</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2678,31 +2678,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536061</v>
+        <v>535988</v>
       </c>
       <c r="R18" t="n">
-        <v>6663870</v>
+        <v>6663825</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121377626</v>
+        <v>121380829</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>90667</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,52 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536173</v>
+        <v>536023</v>
       </c>
       <c r="R3" t="n">
-        <v>6663536</v>
+        <v>6663863</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +883,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -918,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121380560</v>
+        <v>121377626</v>
       </c>
       <c r="B4" t="n">
-        <v>74527</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,41 +926,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536014</v>
+        <v>536173</v>
       </c>
       <c r="R4" t="n">
-        <v>6663853</v>
+        <v>6663536</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1013,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov klibbal 54 cm i diameter.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,21 +1029,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1050,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121381766</v>
+        <v>121377312</v>
       </c>
       <c r="B5" t="n">
-        <v>74654</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,41 +1057,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536080</v>
+        <v>536183</v>
       </c>
       <c r="R5" t="n">
-        <v>6663854</v>
+        <v>6663507</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På död gran.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,21 +1151,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1182,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121377665</v>
+        <v>121400778</v>
       </c>
       <c r="B6" t="n">
-        <v>56409</v>
+        <v>77545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,47 +1179,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100045</v>
+        <v>6000248</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536173</v>
+        <v>536121</v>
       </c>
       <c r="R6" t="n">
-        <v>6663536</v>
+        <v>6663736</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1261,22 +1240,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,28 +1259,49 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121379027</v>
+        <v>121381773</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>57725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,41 +1310,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536126</v>
+        <v>536080</v>
       </c>
       <c r="R7" t="n">
-        <v>6663835</v>
+        <v>6663854</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,7 +1382,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1388,12 +1392,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Vid stort block.</t>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,7 +1417,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1659,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121381754</v>
+        <v>121379027</v>
       </c>
       <c r="B10" t="n">
-        <v>5172</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,43 +1675,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536061</v>
+        <v>536126</v>
       </c>
       <c r="R10" t="n">
-        <v>6663870</v>
+        <v>6663835</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1739,7 +1738,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,12 +1748,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>Snitslat av SKS. Vid stort block.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121380829</v>
+        <v>121381766</v>
       </c>
       <c r="B11" t="n">
-        <v>90667</v>
+        <v>74654</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1793,25 +1792,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1821,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536023</v>
+        <v>536080</v>
       </c>
       <c r="R11" t="n">
-        <v>6663863</v>
+        <v>6663854</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1856,7 +1855,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1866,7 +1865,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1908,10 +1912,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121381773</v>
+        <v>121379915</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,47 +1924,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536080</v>
+        <v>536016</v>
       </c>
       <c r="R12" t="n">
-        <v>6663854</v>
+        <v>6663828</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1992,7 +1987,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2002,12 +1997,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I sumpskog.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,14 +2022,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121379915</v>
+        <v>121379825</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536016</v>
+        <v>536119</v>
       </c>
       <c r="R13" t="n">
-        <v>6663828</v>
+        <v>6663816</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2109,7 +2104,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2119,12 +2114,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2151,10 +2146,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121377312</v>
+        <v>121381754</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>5172</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2163,31 +2158,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2196,13 +2191,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536183</v>
+        <v>536061</v>
       </c>
       <c r="R14" t="n">
-        <v>6663507</v>
+        <v>6663870</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2231,7 +2226,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2241,12 +2236,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>3 fröställningar.</t>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2273,10 +2268,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121379825</v>
+        <v>121400775</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>77558</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2285,38 +2280,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6003412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Röd kådsvartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis zebrina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Rikkinen &amp; Tuovila</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536119</v>
+        <v>536121</v>
       </c>
       <c r="R15" t="n">
-        <v>6663816</v>
+        <v>6663736</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2343,27 +2341,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Snitslat av SKS.</t>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,28 +2360,49 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121378966</v>
+        <v>121377665</v>
       </c>
       <c r="B16" t="n">
-        <v>77545</v>
+        <v>56409</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2402,41 +2411,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6000248</v>
+        <v>100045</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536122</v>
+        <v>536173</v>
       </c>
       <c r="R16" t="n">
-        <v>6663736</v>
+        <v>6663536</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2468,7 +2483,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2478,12 +2493,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2492,35 +2502,10 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -2535,10 +2520,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121400778</v>
+        <v>121379908</v>
       </c>
       <c r="B17" t="n">
-        <v>77545</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2547,44 +2532,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6000248</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536121</v>
+        <v>535988</v>
       </c>
       <c r="R17" t="n">
-        <v>6663736</v>
+        <v>6663825</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2608,17 +2595,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2627,49 +2624,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121379908</v>
+        <v>121380560</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>74527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2678,43 +2654,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535988</v>
+        <v>536014</v>
       </c>
       <c r="R18" t="n">
-        <v>6663825</v>
+        <v>6663853</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2746,7 +2717,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2756,12 +2727,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Snitslat av SKS. Utanför Gysinge Skogs NV-gräns.</t>
+          <t>På grov klibbal 54 cm i diameter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2772,6 +2743,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2788,10 +2774,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121400775</v>
+        <v>121378966</v>
       </c>
       <c r="B19" t="n">
-        <v>77558</v>
+        <v>77545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2804,21 +2790,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003412</v>
+        <v>6000248</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Röd kådsvartspik</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis zebrina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Rikkinen &amp; Tuovila</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2831,7 +2817,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536121</v>
+        <v>536122</v>
       </c>
       <c r="R19" t="n">
         <v>6663736</v>
@@ -2861,17 +2847,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2884,35 +2880,39 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>kåda # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr"/>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121377626</v>
+        <v>121400778</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>77545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,52 +926,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6000248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536173</v>
+        <v>536121</v>
       </c>
       <c r="R4" t="n">
-        <v>6663536</v>
+        <v>6663736</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,27 +987,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,25 +1006,46 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121377312</v>
+        <v>121377626</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1078,7 +1078,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1090,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536183</v>
+        <v>536173</v>
       </c>
       <c r="R5" t="n">
-        <v>6663507</v>
+        <v>6663536</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,12 +1144,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3 fröställningar.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1176,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121400778</v>
+        <v>121377312</v>
       </c>
       <c r="B6" t="n">
-        <v>77545</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,44 +1188,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6000248</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536121</v>
+        <v>536183</v>
       </c>
       <c r="R6" t="n">
-        <v>6663736</v>
+        <v>6663507</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,17 +1251,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,39 +1280,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121400778</v>
+        <v>121377626</v>
       </c>
       <c r="B4" t="n">
-        <v>77545</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,41 +926,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6000248</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536121</v>
+        <v>536173</v>
       </c>
       <c r="R4" t="n">
-        <v>6663736</v>
+        <v>6663536</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,17 +998,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,46 +1027,25 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121377626</v>
+        <v>121377312</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1078,16 +1078,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -1099,13 +1090,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536173</v>
+        <v>536183</v>
       </c>
       <c r="R5" t="n">
-        <v>6663536</v>
+        <v>6663507</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,12 +1135,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121377312</v>
+        <v>121400778</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>77545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,46 +1179,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6000248</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536183</v>
+        <v>536121</v>
       </c>
       <c r="R6" t="n">
-        <v>6663507</v>
+        <v>6663736</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,27 +1240,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3 fröställningar.</t>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,18 +1259,39 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79084065</v>
+        <v>121380829</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536240.0918503734</v>
+        <v>536023</v>
       </c>
       <c r="R2" t="n">
-        <v>6663581.211669928</v>
+        <v>6663863</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +766,41 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristoffer Hylander</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristoffer Hylander</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121381773</v>
+        <v>121381688</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,43 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536080</v>
+        <v>536047</v>
       </c>
       <c r="R3" t="n">
-        <v>6663854</v>
+        <v>6663867</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I sumpskog.</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,6 +888,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -906,44 +912,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog, Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121381688</v>
+        <v>121381766</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536047</v>
+        <v>536080</v>
       </c>
       <c r="R4" t="n">
-        <v>6663867</v>
+        <v>6663854</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På död gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,53 +1046,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121379825</v>
+        <v>121379920</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536119</v>
+        <v>535986</v>
       </c>
       <c r="R5" t="n">
-        <v>6663816</v>
+        <v>6663849</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Snitslat av SKS.</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,8 +1138,24 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1160,12 +1175,7 @@
         <v>121380560</v>
       </c>
       <c r="B6" t="n">
-        <v>74534</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,43 +1299,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121377312</v>
+        <v>121377665</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,13 +1343,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536183</v>
+        <v>536173</v>
       </c>
       <c r="R7" t="n">
-        <v>6663507</v>
+        <v>6663536</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,7 +1378,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,12 +1388,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3 fröställningar.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,56 +1415,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121400778</v>
+        <v>121381754</v>
       </c>
       <c r="B8" t="n">
-        <v>77552</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6000248</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536121</v>
+        <v>536061</v>
       </c>
       <c r="R8" t="n">
-        <v>6663736</v>
+        <v>6663870</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,17 +1485,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
+          <t>På senvuxen gran i sumpskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,89 +1514,68 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121379915</v>
+        <v>121379200</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536016</v>
+        <v>536184</v>
       </c>
       <c r="R9" t="n">
-        <v>6663828</v>
+        <v>6663844</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1617,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1627,12 +1617,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Knärot. Snitslat av SKS</t>
+          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,15 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121381766</v>
+        <v>121377259</v>
       </c>
       <c r="B10" t="n">
-        <v>74661</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,21 +1660,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1699,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536080</v>
+        <v>536132</v>
       </c>
       <c r="R10" t="n">
-        <v>6663854</v>
+        <v>6663471</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1734,7 +1719,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1744,12 +1729,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På död gran.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,21 +1740,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1791,15 +1756,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121377665</v>
+        <v>121381773</v>
       </c>
       <c r="B11" t="n">
-        <v>56410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,16 +1767,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100045</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1826,12 +1786,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1840,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536173</v>
+        <v>536080</v>
       </c>
       <c r="R11" t="n">
-        <v>6663536</v>
+        <v>6663854</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1875,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1885,7 +1845,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I sumpskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,22 +1870,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121377626</v>
+        <v>79084065</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,34 +1905,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536173</v>
+        <v>536240</v>
       </c>
       <c r="R12" t="n">
-        <v>6663536</v>
+        <v>6663581</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1996,27 +1942,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En vinterståndare. Fler plantor.</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2031,68 +1962,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Kristoffer Hylander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Kristoffer Hylander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121400775</v>
+        <v>121377312</v>
       </c>
       <c r="B13" t="n">
-        <v>77565</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003412</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Röd kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis zebrina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Rikkinen &amp; Tuovila</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536121</v>
+        <v>536183</v>
       </c>
       <c r="R13" t="n">
-        <v>6663736</v>
+        <v>6663507</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2116,17 +2044,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
+          <t>3 fröställningar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,82 +2073,65 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>kåda # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121381754</v>
+        <v>121377626</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2219,13 +2140,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536061</v>
+        <v>536173</v>
       </c>
       <c r="R14" t="n">
-        <v>6663870</v>
+        <v>6663536</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2254,7 +2175,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2264,12 +2185,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog.</t>
+          <t>En vinterståndare. Fler plantor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2299,12 +2220,7 @@
         <v>121379027</v>
       </c>
       <c r="B15" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2413,37 +2329,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121377259</v>
+        <v>121379825</v>
       </c>
       <c r="B16" t="n">
-        <v>57726</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2453,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536132</v>
+        <v>536119</v>
       </c>
       <c r="R16" t="n">
-        <v>6663471</v>
+        <v>6663816</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2488,7 +2399,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2498,7 +2409,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Snitslat av SKS.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2528,12 +2444,7 @@
         <v>121379908</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2647,53 +2558,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121378966</v>
+        <v>121379915</v>
       </c>
       <c r="B18" t="n">
-        <v>77552</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6000248</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536122</v>
+        <v>536016</v>
       </c>
       <c r="R18" t="n">
-        <v>6663736</v>
+        <v>6663828</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2725,7 +2628,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2735,12 +2638,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
+          <t>Knärot. Snitslat av SKS</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2749,35 +2652,10 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Grankåda.</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+      <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -2792,50 +2670,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121380829</v>
+        <v>121378966</v>
       </c>
       <c r="B19" t="n">
-        <v>90675</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>6000248</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536023</v>
+        <v>536122</v>
       </c>
       <c r="R19" t="n">
-        <v>6663863</v>
+        <v>6663736</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2867,7 +2743,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2877,7 +2753,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På grankåda i lång stamskada på ganska klen gran. Barrblandskog, tydligt skogsbrukspåverkad och under 100 år. Skogen har gallrats någon gång och många träd uppvisar stamskador (med kådutgjutningar), gissningsvis uppkomna i samband med gallringen. Mikroskopierad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2886,25 +2767,35 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr"/>
+          <t>Grankåda.</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="AW19" t="inlineStr">
         <is>
           <t>Uno Skog</t>
@@ -2919,37 +2810,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121379920</v>
+        <v>121400778</v>
       </c>
       <c r="B20" t="n">
-        <v>74534</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6428</v>
+        <v>6000248</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2962,13 +2848,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535986</v>
+        <v>536121</v>
       </c>
       <c r="R20" t="n">
-        <v>6663849</v>
+        <v>6663736</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2992,22 +2878,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mest mörk kådsvartspik, men även Chaenothecopsis zebrina.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3020,85 +2901,83 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>kåda # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121379200</v>
+        <v>121400775</v>
       </c>
       <c r="B21" t="n">
-        <v>43712</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101735</v>
+        <v>6003412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Röd kådsvartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaenothecopsis zebrina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Rikkinen &amp; Tuovila</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ungsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536184</v>
+        <v>536121</v>
       </c>
       <c r="R21" t="n">
-        <v>6663844</v>
+        <v>6663736</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3125,27 +3004,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Kläckhål I flera stora fnösktickor. Både på högstubbe och på liggande lågor i tickor som växt sedan stammarna föll. Kan vara pågående gnag fortfarande.</t>
+          <t>Kåda i en 1 kvadratdecimeter stor skada. Tillsammans med Chaenothecopsis Montana. Mikroskoperad K+ röd.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,18 +3023,39 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>kåda # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 42272-2021 artfynd.xlsx
+++ b/artfynd/A 42272-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121380829</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121381688</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121381766</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,6 +1189,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379920</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1296,6 +1321,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121380560</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1412,6 +1442,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121377665</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1529,6 +1564,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121381754</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1646,6 +1686,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379200</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1753,6 +1798,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121377259</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1874,6 +1924,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121381773</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1971,6 +2026,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79084065</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2088,6 +2148,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121377312</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2214,6 +2279,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121377626</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2326,6 +2396,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379027</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2438,6 +2513,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379825</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2555,6 +2635,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379908</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2667,6 +2752,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121379915</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2807,6 +2897,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121378966</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2933,6 +3028,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121400778</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,8 +3159,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121400775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>